--- a/finance/output/SP500_Financial_Metrics_20250429_162048.xlsx
+++ b/finance/output/SP500_Financial_Metrics_20250429_162048.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\finance_script\finance\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D629A48C-7DEA-4F08-885F-24A3708949EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E04BD8B-EE55-48F8-B4A9-C24E89124131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
